--- a/docs/templates/mock_drive/2026001 — Rockland/budget/2026001_BUDGET_v1.xlsx
+++ b/docs/templates/mock_drive/2026001 — Rockland/budget/2026001_BUDGET_v1.xlsx
@@ -841,9 +841,10 @@
           <t>Client_Price_Pre_Global</t>
         </is>
       </c>
-      <c r="B3">
-        <f> Budget_Amount x Line_Markup_Factor (per-line inflation only).</f>
-        <v/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Equals Budget_Amount x Line_Markup_Factor (per-line inflation only).</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -852,9 +853,10 @@
           <t>Final Client Price</t>
         </is>
       </c>
-      <c r="B4">
-        <f> SUM(Client_Price_Pre_Global) x 1.15 (global 15% markup applied at subtotal).</f>
-        <v/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Equals SUM(Client_Price_Pre_Global) x 1.15 (global 15% markup applied at subtotal).</t>
+        </is>
       </c>
     </row>
     <row r="5">

--- a/docs/templates/mock_drive/2026001 — Rockland/budget/2026001_BUDGET_v1.xlsx
+++ b/docs/templates/mock_drive/2026001 — Rockland/budget/2026001_BUDGET_v1.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
